--- a/data/Escenarios_DCH_septiembre/Bateria_353/Costo_fijo/Carga_on_board_fixed_3estaciones_P320kW/elmo_data.xlsx
+++ b/data/Escenarios_DCH_septiembre/Bateria_353/Costo_fijo/Carga_on_board_fixed_3estaciones_P320kW/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH_septiembre\Bateria_353\Costo_fijo\Carga_on_board_fixed_3estaciones_P320kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190FA4F1-9309-4183-B5B7-7F9771024DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16975CD8-7C99-405C-93CE-A5E845743C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="3840" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC3">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -2334,10 +2334,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC4">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
@@ -2423,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC5">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
@@ -2512,10 +2512,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC6">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
@@ -2601,10 +2601,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC7">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
@@ -2690,10 +2690,10 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC8">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
@@ -2779,10 +2779,10 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC9">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
@@ -2868,10 +2868,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC10">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
@@ -2957,10 +2957,10 @@
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC11">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
@@ -3046,10 +3046,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC12">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
@@ -3135,10 +3135,10 @@
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC13">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
@@ -3224,10 +3224,10 @@
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC14">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
